--- a/exports/trend_1d/OIL_full_report.xlsx
+++ b/exports/trend_1d/OIL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>10.15</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42047</v>
+        <v>42048</v>
       </c>
       <c r="H2" t="n">
-        <v>177.65</v>
+        <v>167.15</v>
       </c>
       <c r="I2" t="n">
         <v>169.9109442569115</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.11</v>
+        <v>-6.02</v>
       </c>
       <c r="L2" t="n">
-        <v>1.86</v>
+        <v>6.97</v>
       </c>
       <c r="M2" t="n">
-        <v>0.64</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>3.07</v>
+        <v>5.91</v>
       </c>
       <c r="O2" t="n">
         <v>0.45</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>12.46</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42107</v>
+        <v>42109</v>
       </c>
       <c r="H3" t="n">
-        <v>161</v>
+        <v>167.55</v>
       </c>
       <c r="I3" t="n">
         <v>163.805381661143</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K3" t="n">
-        <v>3.68</v>
+        <v>-0.24</v>
       </c>
       <c r="L3" t="n">
         <v>5.15</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42115</v>
+        <v>42116</v>
       </c>
       <c r="H4" t="n">
-        <v>162.85</v>
+        <v>155.8</v>
       </c>
       <c r="I4" t="n">
         <v>158.3243976829116</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.81</v>
+        <v>-7.01</v>
       </c>
       <c r="L4" t="n">
-        <v>3.91</v>
+        <v>7.85</v>
       </c>
       <c r="M4" t="n">
         <v>0.51</v>
       </c>
       <c r="N4" t="n">
-        <v>3.91</v>
+        <v>4.33</v>
       </c>
       <c r="O4" t="n">
         <v>4.07</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>15.05</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42221</v>
+        <v>42222</v>
       </c>
       <c r="H5" t="n">
-        <v>150.15</v>
+        <v>152.5</v>
       </c>
       <c r="I5" t="n">
         <v>152.0984744702366</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K5" t="n">
-        <v>3.63</v>
+        <v>2.12</v>
       </c>
       <c r="L5" t="n">
         <v>8.06</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>7.98</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H6" t="n">
-        <v>152.35</v>
+        <v>143.3</v>
       </c>
       <c r="I6" t="n">
         <v>144.0269215658853</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1</v>
+        <v>-6.03</v>
       </c>
       <c r="L6" t="n">
-        <v>2.72</v>
+        <v>6.89</v>
       </c>
       <c r="M6" t="n">
-        <v>1.76</v>
+        <v>3.28</v>
       </c>
       <c r="N6" t="n">
-        <v>1.08</v>
+        <v>5.94</v>
       </c>
       <c r="O6" t="n">
         <v>1.57</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.86</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42284</v>
+        <v>42285</v>
       </c>
       <c r="H7" t="n">
-        <v>152.2</v>
+        <v>154.85</v>
       </c>
       <c r="I7" t="n">
         <v>153.3805819847084</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.21</v>
+        <v>-8.06</v>
       </c>
       <c r="L7" t="n">
         <v>10.75</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>9</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42300</v>
+        <v>42303</v>
       </c>
       <c r="H8" t="n">
-        <v>145.3</v>
+        <v>139.4</v>
       </c>
       <c r="I8" t="n">
         <v>141.0607185044646</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K8" t="n">
-        <v>-6.17</v>
+        <v>-9.98</v>
       </c>
       <c r="L8" t="n">
-        <v>6.88</v>
+        <v>10.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0.27</v>
+        <v>0.58</v>
       </c>
       <c r="N8" t="n">
-        <v>1.84</v>
+        <v>4.06</v>
       </c>
       <c r="O8" t="n">
         <v>1.74</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.83</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42362</v>
+        <v>42366</v>
       </c>
       <c r="H9" t="n">
-        <v>129.5</v>
+        <v>133.55</v>
       </c>
       <c r="I9" t="n">
         <v>132.1089944655221</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K9" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
         <v>4.02</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>9.59</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42381</v>
+        <v>42382</v>
       </c>
       <c r="H10" t="n">
-        <v>125.1</v>
+        <v>121.25</v>
       </c>
       <c r="I10" t="n">
         <v>121.9194663466927</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.33</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>8.84</v>
+        <v>10.11</v>
       </c>
       <c r="M10" t="n">
         <v>2.24</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>12.96</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42487</v>
+        <v>42488</v>
       </c>
       <c r="H11" t="n">
-        <v>109.55</v>
+        <v>110.55</v>
       </c>
       <c r="I11" t="n">
         <v>109.7521045491217</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K11" t="n">
-        <v>9.65</v>
+        <v>8.82</v>
       </c>
       <c r="L11" t="n">
         <v>4.33</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.53</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42752</v>
+        <v>42753</v>
       </c>
       <c r="H12" t="n">
-        <v>151.9</v>
+        <v>149.45</v>
       </c>
       <c r="I12" t="n">
         <v>151.3505534482573</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K12" t="n">
-        <v>37.4</v>
+        <v>35.19</v>
       </c>
       <c r="L12" t="n">
         <v>3.39</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>181</v>
+        <v>182</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>9</v>
+      </c>
+      <c r="U12" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.59</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42934</v>
+        <v>42935</v>
       </c>
       <c r="H13" t="n">
-        <v>123.4</v>
+        <v>126</v>
       </c>
       <c r="I13" t="n">
         <v>125.0922137656584</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K13" t="n">
-        <v>17.43</v>
+        <v>15.69</v>
       </c>
       <c r="L13" t="n">
         <v>4.52</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>7</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.66</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43129</v>
+        <v>43130</v>
       </c>
       <c r="H14" t="n">
-        <v>162.85</v>
+        <v>159.75</v>
       </c>
       <c r="I14" t="n">
         <v>160.1257087517806</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K14" t="n">
-        <v>29.25</v>
+        <v>26.79</v>
       </c>
       <c r="L14" t="n">
         <v>4.6</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43213</v>
+        <v>43214</v>
       </c>
       <c r="H15" t="n">
-        <v>154.4</v>
+        <v>158.05</v>
       </c>
       <c r="I15" t="n">
         <v>157.0534726123147</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K15" t="n">
-        <v>3.35</v>
+        <v>1.06</v>
       </c>
       <c r="L15" t="n">
         <v>2.66</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>8.44</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43243</v>
+        <v>43244</v>
       </c>
       <c r="H16" t="n">
-        <v>153.95</v>
+        <v>143.75</v>
       </c>
       <c r="I16" t="n">
         <v>149.4835426368438</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.59</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>7.28</v>
+        <v>13.98</v>
       </c>
       <c r="M16" t="n">
         <v>0.88</v>
       </c>
       <c r="N16" t="n">
-        <v>4.58</v>
+        <v>6.63</v>
       </c>
       <c r="O16" t="n">
         <v>2.36</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>14.51</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43362</v>
+        <v>43364</v>
       </c>
       <c r="H17" t="n">
-        <v>138.65</v>
+        <v>145.75</v>
       </c>
       <c r="I17" t="n">
         <v>144.1223730771098</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K17" t="n">
-        <v>3.55</v>
+        <v>-1.39</v>
       </c>
       <c r="L17" t="n">
         <v>8.07</v>
@@ -1410,7 +1613,7 @@
         <v>1.98</v>
       </c>
       <c r="N17" t="n">
-        <v>4.29</v>
+        <v>5.12</v>
       </c>
       <c r="O17" t="n">
         <v>-6.63</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43377</v>
+        <v>43378</v>
       </c>
       <c r="H18" t="n">
-        <v>139.35</v>
+        <v>124.6</v>
       </c>
       <c r="I18" t="n">
         <v>136.3470473545277</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.39</v>
+        <v>-14.51</v>
       </c>
       <c r="L18" t="n">
-        <v>8.710000000000001</v>
+        <v>17.22</v>
       </c>
       <c r="M18" t="n">
-        <v>0.71</v>
+        <v>5.24</v>
       </c>
       <c r="N18" t="n">
-        <v>5.17</v>
+        <v>10.58</v>
       </c>
       <c r="O18" t="n">
         <v>5.12</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>18.73</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43515</v>
+        <v>43516</v>
       </c>
       <c r="H19" t="n">
-        <v>118.05</v>
+        <v>120.15</v>
       </c>
       <c r="I19" t="n">
         <v>119.1453917662555</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K19" t="n">
-        <v>5.26</v>
+        <v>3.57</v>
       </c>
       <c r="L19" t="n">
         <v>13.44</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>7.64</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H20" t="n">
-        <v>115.65</v>
+        <v>111.25</v>
       </c>
       <c r="I20" t="n">
         <v>115.2391959813653</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.75</v>
+        <v>-7.41</v>
       </c>
       <c r="L20" t="n">
-        <v>6.12</v>
+        <v>8.24</v>
       </c>
       <c r="M20" t="n">
         <v>4.58</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.57</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43752</v>
+        <v>43753</v>
       </c>
       <c r="H21" t="n">
-        <v>102.15</v>
+        <v>105.6</v>
       </c>
       <c r="I21" t="n">
         <v>104.9302960528119</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K21" t="n">
-        <v>8.18</v>
+        <v>5.08</v>
       </c>
       <c r="L21" t="n">
         <v>7.37</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>11.19</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43790</v>
+        <v>43791</v>
       </c>
       <c r="H22" t="n">
-        <v>103.4</v>
+        <v>102.6</v>
       </c>
       <c r="I22" t="n">
         <v>102.8389121959454</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.08</v>
+        <v>-2.84</v>
       </c>
       <c r="L22" t="n">
-        <v>3.93</v>
+        <v>5.26</v>
       </c>
       <c r="M22" t="n">
         <v>0.48</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>9.99</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43867</v>
+        <v>43868</v>
       </c>
       <c r="H23" t="n">
-        <v>90.05</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>91.7251775824642</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K23" t="n">
-        <v>12.23</v>
+        <v>9.99</v>
       </c>
       <c r="L23" t="n">
         <v>3.95</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>13.85</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43885</v>
+        <v>43886</v>
       </c>
       <c r="H24" t="n">
-        <v>80.3</v>
+        <v>78.45</v>
       </c>
       <c r="I24" t="n">
         <v>79.67074432535787</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K24" t="n">
-        <v>-13.05</v>
+        <v>-15.05</v>
       </c>
       <c r="L24" t="n">
-        <v>13.37</v>
+        <v>15.21</v>
       </c>
       <c r="M24" t="n">
         <v>7.42</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>17.18</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43950</v>
+        <v>43951</v>
       </c>
       <c r="H25" t="n">
-        <v>61.15</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>65.50456646151822</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K25" t="n">
-        <v>22.05</v>
+        <v>16.06</v>
       </c>
       <c r="L25" t="n">
         <v>3.44</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>21.71</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44082</v>
+        <v>44083</v>
       </c>
       <c r="H26" t="n">
-        <v>63.1</v>
+        <v>62.25</v>
       </c>
       <c r="I26" t="n">
         <v>62.63980727109636</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.18</v>
+        <v>-5.47</v>
       </c>
       <c r="L26" t="n">
         <v>30.14</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>7.09</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44146</v>
+        <v>44147</v>
       </c>
       <c r="H27" t="n">
-        <v>60.35</v>
+        <v>61.25</v>
       </c>
       <c r="I27" t="n">
         <v>61.06368152989702</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K27" t="n">
-        <v>3.05</v>
+        <v>1.61</v>
       </c>
       <c r="L27" t="n">
         <v>4.9</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>7.24</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H28" t="n">
-        <v>72.75</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="I28" t="n">
         <v>69.10602002525263</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K28" t="n">
-        <v>18.78</v>
+        <v>10.78</v>
       </c>
       <c r="L28" t="n">
         <v>1.96</v>
@@ -2037,7 +2372,7 @@
         <v>1.48</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>6.74</v>
       </c>
       <c r="O28" t="n">
         <v>1.49</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>17.14</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44210</v>
+        <v>44211</v>
       </c>
       <c r="H29" t="n">
-        <v>78.09999999999999</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="I29" t="n">
         <v>78.16717026143176</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K29" t="n">
-        <v>-15.11</v>
+        <v>-15.48</v>
       </c>
       <c r="L29" t="n">
         <v>17.32</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44273</v>
+        <v>44274</v>
       </c>
       <c r="H30" t="n">
-        <v>84.95</v>
+        <v>79.75</v>
       </c>
       <c r="I30" t="n">
         <v>80.77606522967507</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K30" t="n">
-        <v>8.42</v>
+        <v>1.79</v>
       </c>
       <c r="L30" t="n">
         <v>7.66</v>
       </c>
       <c r="M30" t="n">
-        <v>2.13</v>
+        <v>3.47</v>
       </c>
       <c r="N30" t="n">
-        <v>3.56</v>
+        <v>6.12</v>
       </c>
       <c r="O30" t="n">
         <v>0.32</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>12.41</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44326</v>
+        <v>44327</v>
       </c>
       <c r="H31" t="n">
-        <v>84.45</v>
+        <v>86.3</v>
       </c>
       <c r="I31" t="n">
         <v>84.48142551473531</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.89</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="L31" t="n">
         <v>10.91</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>10.05</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44392</v>
+        <v>44393</v>
       </c>
       <c r="H32" t="n">
-        <v>107.55</v>
+        <v>104.45</v>
       </c>
       <c r="I32" t="n">
         <v>105.3357973053463</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K32" t="n">
-        <v>24.62</v>
+        <v>21.03</v>
       </c>
       <c r="L32" t="n">
         <v>2.95</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>12.04</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44431</v>
+        <v>44432</v>
       </c>
       <c r="H33" t="n">
-        <v>112.1</v>
+        <v>114.05</v>
       </c>
       <c r="I33" t="n">
         <v>113.7679829698245</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K33" t="n">
-        <v>-7.32</v>
+        <v>-9.19</v>
       </c>
       <c r="L33" t="n">
         <v>9.77</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10.39</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44489</v>
+        <v>44490</v>
       </c>
       <c r="H34" t="n">
-        <v>152.25</v>
+        <v>144.65</v>
       </c>
       <c r="I34" t="n">
         <v>149.6728258956233</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K34" t="n">
-        <v>33.49</v>
+        <v>26.83</v>
       </c>
       <c r="L34" t="n">
         <v>1.14</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>17.9</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44559</v>
+        <v>44560</v>
       </c>
       <c r="H35" t="n">
-        <v>123.35</v>
+        <v>134.4</v>
       </c>
       <c r="I35" t="n">
         <v>132.2288336635148</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K35" t="n">
-        <v>14.73</v>
+        <v>7.09</v>
       </c>
       <c r="L35" t="n">
         <v>7.88</v>
@@ -2436,7 +2855,7 @@
         <v>2.98</v>
       </c>
       <c r="N35" t="n">
-        <v>7.52</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O35" t="n">
         <v>-4.99</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>16.5</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H36" t="n">
-        <v>156.2</v>
+        <v>146.6</v>
       </c>
       <c r="I36" t="n">
         <v>147.46073253889</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K36" t="n">
-        <v>16.22</v>
+        <v>9.08</v>
       </c>
       <c r="L36" t="n">
         <v>7.4</v>
@@ -2493,7 +2924,7 @@
         <v>2.21</v>
       </c>
       <c r="N36" t="n">
-        <v>3.33</v>
+        <v>6.15</v>
       </c>
       <c r="O36" t="n">
         <v>8.960000000000001</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>19.14</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44713</v>
+        <v>44714</v>
       </c>
       <c r="H37" t="n">
-        <v>163.25</v>
+        <v>166.9</v>
       </c>
       <c r="I37" t="n">
         <v>165.9739114402025</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K37" t="n">
-        <v>-11.36</v>
+        <v>-13.85</v>
       </c>
       <c r="L37" t="n">
-        <v>14.15</v>
+        <v>14.84</v>
       </c>
       <c r="M37" t="n">
         <v>3.65</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>15.27</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44729</v>
+        <v>44732</v>
       </c>
       <c r="H38" t="n">
-        <v>169.75</v>
+        <v>151.35</v>
       </c>
       <c r="I38" t="n">
         <v>168.8193176244</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K38" t="n">
-        <v>1.71</v>
+        <v>-9.32</v>
       </c>
       <c r="L38" t="n">
-        <v>4.1</v>
+        <v>12.73</v>
       </c>
       <c r="M38" t="n">
-        <v>2.2</v>
+        <v>3.39</v>
       </c>
       <c r="N38" t="n">
-        <v>5.8</v>
+        <v>10.84</v>
       </c>
       <c r="O38" t="n">
         <v>2.24</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>27.3</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44840</v>
+        <v>44841</v>
       </c>
       <c r="H39" t="n">
-        <v>124.65</v>
+        <v>125.35</v>
       </c>
       <c r="I39" t="n">
         <v>124.940047170003</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K39" t="n">
-        <v>17.64</v>
+        <v>17.18</v>
       </c>
       <c r="L39" t="n">
         <v>16.06</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H40" t="n">
-        <v>135.35</v>
+        <v>132.55</v>
       </c>
       <c r="I40" t="n">
         <v>133.3829931433561</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K40" t="n">
-        <v>7.98</v>
+        <v>5.74</v>
       </c>
       <c r="L40" t="n">
         <v>3.31</v>
       </c>
       <c r="M40" t="n">
-        <v>1.45</v>
+        <v>1.92</v>
       </c>
       <c r="N40" t="n">
         <v>3.22</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>8.92</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44936</v>
+        <v>44937</v>
       </c>
       <c r="H41" t="n">
-        <v>142.65</v>
+        <v>148.55</v>
       </c>
       <c r="I41" t="n">
         <v>144.3702558787796</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.62</v>
+        <v>-12.07</v>
       </c>
       <c r="L41" t="n">
-        <v>8.640000000000001</v>
+        <v>13.13</v>
       </c>
       <c r="M41" t="n">
         <v>0.52</v>
       </c>
       <c r="N41" t="n">
-        <v>3.9</v>
+        <v>4.14</v>
       </c>
       <c r="O41" t="n">
         <v>-2.07</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44959</v>
+        <v>44960</v>
       </c>
       <c r="H42" t="n">
-        <v>150.25</v>
+        <v>144.2</v>
       </c>
       <c r="I42" t="n">
         <v>148.6171418458097</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K42" t="n">
-        <v>1.14</v>
+        <v>-2.93</v>
       </c>
       <c r="L42" t="n">
         <v>3.97</v>
@@ -2835,7 +3338,7 @@
         <v>1.04</v>
       </c>
       <c r="N42" t="n">
-        <v>3.51</v>
+        <v>4.03</v>
       </c>
       <c r="O42" t="n">
         <v>4.14</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>12.93</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44967</v>
+        <v>44970</v>
       </c>
       <c r="H43" t="n">
-        <v>149.05</v>
+        <v>160.65</v>
       </c>
       <c r="I43" t="n">
         <v>158.53580986196</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.36</v>
+        <v>-11.41</v>
       </c>
       <c r="L43" t="n">
-        <v>8.359999999999999</v>
+        <v>12.34</v>
       </c>
       <c r="M43" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="N43" t="n">
-        <v>4.49</v>
+        <v>7.78</v>
       </c>
       <c r="O43" t="n">
         <v>-4.03</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>12.54</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45078</v>
+        <v>45079</v>
       </c>
       <c r="H44" t="n">
-        <v>169.5</v>
+        <v>166.65</v>
       </c>
       <c r="I44" t="n">
         <v>167.1609845613014</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K44" t="n">
-        <v>5.51</v>
+        <v>3.73</v>
       </c>
       <c r="L44" t="n">
         <v>3.24</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>8.98</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45127</v>
+        <v>45128</v>
       </c>
       <c r="H45" t="n">
-        <v>171.25</v>
+        <v>172.05</v>
       </c>
       <c r="I45" t="n">
         <v>171.3707525581174</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.76</v>
+        <v>-3.24</v>
       </c>
       <c r="L45" t="n">
         <v>3.42</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>4.73</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45168</v>
+        <v>45169</v>
       </c>
       <c r="H46" t="n">
-        <v>183.95</v>
+        <v>182.05</v>
       </c>
       <c r="I46" t="n">
         <v>182.7239573569971</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K46" t="n">
-        <v>6.92</v>
+        <v>5.81</v>
       </c>
       <c r="L46" t="n">
         <v>0.99</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.64</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45197</v>
+        <v>45198</v>
       </c>
       <c r="H47" t="n">
-        <v>194.85</v>
+        <v>199.25</v>
       </c>
       <c r="I47" t="n">
         <v>195.9535911532401</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K47" t="n">
-        <v>-7.03</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="L47" t="n">
         <v>11.86</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>10.61</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45229</v>
+        <v>45230</v>
       </c>
       <c r="H48" t="n">
-        <v>202.55</v>
+        <v>199.25</v>
       </c>
       <c r="I48" t="n">
         <v>199.2602720703425</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K48" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>3.16</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>11.62</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45261</v>
+        <v>45264</v>
       </c>
       <c r="H49" t="n">
-        <v>206.6</v>
+        <v>218.8</v>
       </c>
       <c r="I49" t="n">
         <v>217.7688837939688</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.69</v>
+        <v>-9.81</v>
       </c>
       <c r="L49" t="n">
-        <v>9.84</v>
+        <v>12.25</v>
       </c>
       <c r="M49" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="N49" t="n">
-        <v>3.89</v>
+        <v>5.91</v>
       </c>
       <c r="O49" t="n">
         <v>-1.63</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>12.79</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H50" t="n">
-        <v>446.25</v>
+        <v>396.35</v>
       </c>
       <c r="I50" t="n">
         <v>398.9151566521373</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K50" t="n">
-        <v>103.95</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="L50" t="n">
         <v>5.96</v>
@@ -3291,7 +3890,7 @@
         <v>1.3</v>
       </c>
       <c r="N50" t="n">
-        <v>9.15</v>
+        <v>11.18</v>
       </c>
       <c r="O50" t="n">
         <v>5.91</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>7</v>
+      </c>
+      <c r="U50" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>19.92</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45456</v>
+        <v>45457</v>
       </c>
       <c r="H51" t="n">
-        <v>451.9</v>
+        <v>466.3</v>
       </c>
       <c r="I51" t="n">
         <v>465.6879145677684</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K51" t="n">
-        <v>-14.02</v>
+        <v>-17.65</v>
       </c>
       <c r="L51" t="n">
-        <v>15.44</v>
+        <v>19.25</v>
       </c>
       <c r="M51" t="n">
         <v>1.93</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>16.43</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H52" t="n">
-        <v>654.9</v>
+        <v>626.95</v>
       </c>
       <c r="I52" t="n">
         <v>650.796586442095</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K52" t="n">
-        <v>40.45</v>
+        <v>34.45</v>
       </c>
       <c r="L52" t="n">
         <v>4.21</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>19.2</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="H53" t="n">
-        <v>463.3</v>
+        <v>481.1</v>
       </c>
       <c r="I53" t="n">
         <v>464.9607579519312</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K53" t="n">
-        <v>26.1</v>
+        <v>23.26</v>
       </c>
       <c r="L53" t="n">
         <v>6.22</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>5</v>
+      </c>
+      <c r="U53" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>11</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45680</v>
+        <v>45681</v>
       </c>
       <c r="H54" t="n">
-        <v>451.3</v>
+        <v>424.5</v>
       </c>
       <c r="I54" t="n">
         <v>428.1836652869642</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K54" t="n">
-        <v>-6.19</v>
+        <v>-11.76</v>
       </c>
       <c r="L54" t="n">
-        <v>8.08</v>
+        <v>12.07</v>
       </c>
       <c r="M54" t="n">
         <v>0.51</v>
       </c>
       <c r="N54" t="n">
-        <v>5.02</v>
+        <v>5.94</v>
       </c>
       <c r="O54" t="n">
         <v>3.84</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>18.26</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="H55" t="n">
-        <v>384.4</v>
+        <v>395.85</v>
       </c>
       <c r="I55" t="n">
         <v>388.0552559585449</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K55" t="n">
-        <v>9.449999999999999</v>
+        <v>6.75</v>
       </c>
       <c r="L55" t="n">
         <v>6.88</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>12.98</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="H56" t="n">
-        <v>442.3</v>
+        <v>433.4</v>
       </c>
       <c r="I56" t="n">
         <v>440.8721798139916</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K56" t="n">
-        <v>11.73</v>
+        <v>9.49</v>
       </c>
       <c r="L56" t="n">
         <v>3.66</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>10.94</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="H57" t="n">
-        <v>414.7</v>
+        <v>419.2</v>
       </c>
       <c r="I57" t="n">
         <v>417.567968152708</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K57" t="n">
-        <v>4.31</v>
+        <v>3.28</v>
       </c>
       <c r="L57" t="n">
         <v>5.21</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.11</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="H58" t="n">
-        <v>417.2</v>
+        <v>413.2</v>
       </c>
       <c r="I58" t="n">
         <v>414.5435428632365</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.48</v>
+        <v>-1.43</v>
       </c>
       <c r="L58" t="n">
         <v>3.39</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>7.05</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="H59" t="n">
-        <v>411.45</v>
+        <v>424.35</v>
       </c>
       <c r="I59" t="n">
         <v>422.4981558480666</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K59" t="n">
-        <v>0.42</v>
+        <v>-2.7</v>
       </c>
       <c r="L59" t="n">
-        <v>1.65</v>
+        <v>3.92</v>
       </c>
       <c r="M59" t="n">
         <v>0.89</v>
       </c>
       <c r="N59" t="n">
-        <v>1.3</v>
+        <v>3.14</v>
       </c>
       <c r="O59" t="n">
         <v>-0.96</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.09</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="H60" t="n">
-        <v>474.85</v>
+        <v>455.25</v>
       </c>
       <c r="I60" t="n">
         <v>455.302328295354</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K60" t="n">
-        <v>11.9</v>
+        <v>7.28</v>
       </c>
       <c r="L60" t="n">
         <v>4.24</v>
@@ -3861,7 +4580,7 @@
         <v>2.35</v>
       </c>
       <c r="N60" t="n">
-        <v>3.69</v>
+        <v>4.13</v>
       </c>
       <c r="O60" t="n">
         <v>3.14</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>13.93</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H61" t="n">
-        <v>490.95</v>
+        <v>507.1</v>
       </c>
       <c r="I61" t="n">
         <v>497.8852731760197</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K61" t="n">
-        <v>-7.84</v>
+        <v>-11.39</v>
       </c>
       <c r="L61" t="n">
-        <v>11.2</v>
+        <v>12.34</v>
       </c>
       <c r="M61" t="n">
         <v>3.95</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>11.28</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H62" t="n">
-        <v>475.95</v>
+        <v>427.35</v>
       </c>
       <c r="I62" t="n">
         <v>469.4434722692134</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K62" t="n">
-        <v>-6.14</v>
+        <v>-15.73</v>
       </c>
       <c r="L62" t="n">
-        <v>7.48</v>
+        <v>16.67</v>
       </c>
       <c r="M62" t="n">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="N62" t="n">
-        <v>3.44</v>
+        <v>10.21</v>
       </c>
       <c r="O62" t="n">
         <v>3.29</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>16.09</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="H63" t="n">
-        <v>435.35</v>
+        <v>453.55</v>
       </c>
       <c r="I63" t="n">
         <v>443.8419464702905</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.87</v>
+        <v>-6.13</v>
       </c>
       <c r="L63" t="n">
         <v>9.42</v>
@@ -4032,7 +4787,7 @@
         <v>1.13</v>
       </c>
       <c r="N63" t="n">
-        <v>2.33</v>
+        <v>4.18</v>
       </c>
       <c r="O63" t="n">
         <v>-10.21</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.74</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="H64" t="n">
-        <v>478.35</v>
+        <v>467</v>
       </c>
       <c r="I64" t="n">
         <v>467.5198423956315</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K64" t="n">
-        <v>5.47</v>
+        <v>2.97</v>
       </c>
       <c r="L64" t="n">
         <v>4</v>
@@ -4089,7 +4856,7 @@
         <v>1.06</v>
       </c>
       <c r="N64" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="O64" t="n">
         <v>4.18</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4149,6 +4928,14 @@
       <c r="Q65" t="n">
         <v>25</v>
       </c>
+      <c r="R65" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9107,7 +9894,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.3</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="6">
@@ -9117,7 +9904,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
@@ -9127,7 +9914,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8">
@@ -9137,7 +9924,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -9147,7 +9934,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85.5</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -9157,7 +9944,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>128.4</v>
+        <v>129.6</v>
       </c>
     </row>
     <row r="11">
@@ -9197,7 +9984,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.13</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="15">
@@ -9207,7 +9994,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.630000000000001</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="16">
@@ -9217,7 +10004,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.51</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="17">
@@ -9227,7 +10014,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>103.95</v>
+        <v>81.15000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -9237,7 +10024,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>57.1</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="19">
@@ -9247,7 +10034,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.95</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -9257,7 +10044,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.96</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="21">
@@ -9277,7 +10064,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -9287,7 +10074,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -9297,7 +10084,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.07</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="25">
@@ -9317,7 +10104,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.88</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="27">
@@ -9337,7 +10124,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
